--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
@@ -9,16 +9,18 @@
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_16">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_223">Hidden_2!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="138">
   <si>
     <t>48978</t>
   </si>
@@ -128,6 +130,9 @@
     <t>436297</t>
   </si>
   <si>
+    <t>571932</t>
+  </si>
+  <si>
     <t>436304</t>
   </si>
   <si>
@@ -221,6 +226,9 @@
     <t>Servidor(a) público(a) y/o área responsable de recibir los resultados</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Total de solventaciones y/o aclaraciones realizadas</t>
   </si>
   <si>
@@ -245,19 +253,47 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
+    <t>Del 01/01/2022 al 31/12/2022</t>
+  </si>
+  <si>
     <t>Auditoría externa</t>
   </si>
   <si>
     <t>Financiera</t>
   </si>
   <si>
+    <t>UAG-AOR-062-2023-29-U006</t>
+  </si>
+  <si>
+    <t>Secretaría de la Función Pública</t>
+  </si>
+  <si>
+    <t>UAG-AOR-062-2023-29-U006 
+CGI2023-09</t>
+  </si>
+  <si>
+    <t>SFCC/200/087/2023</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Participaciones Federales a Entidades Federativas</t>
+  </si>
+  <si>
     <t>Ejercicio y aplicación de los recursos públicos federales, de los capitulo 1000, 2000, 3000, 4000 y 5000.</t>
   </si>
   <si>
-    <t/>
+    <t>Artículo 74 fraccion VI y 79 de la Constitucion Politica de los Estados Unidos Mexicanos; fracciones II, VIII,IX, X, XI, XVI, XVIII y XXX; 6,9,14, fracciones I, III y IV; 17, fracciones I, VI, VII, VIII, XI, XII, XXVI, XXVII y XXVIII; 22, 23, 28, 29, 47, 48, 49, 58 y 67,  y demas relativos de Fiscalizacion y Rendicion de Cuentas de la Federacion; 8, el Presupuesto de Egresos de la Federacion para el ejercicio fiscal 2020, 2, 3, 12 fraccion III del Reglamento Interior de la Auditoria  Superior de la Federacion.</t>
+  </si>
+  <si>
+    <t>Subsidios Federales</t>
   </si>
   <si>
     <t>Dirección Administrativa 
@@ -271,10 +307,42 @@
     <t>Departamento de contabilidad</t>
   </si>
   <si>
+    <t>1877</t>
+  </si>
+  <si>
+    <t>Auditoria Superior de la Federación</t>
+  </si>
+  <si>
+    <t>2022-1877-AFITA 
+1877/2022</t>
+  </si>
+  <si>
+    <t>AEGF/3042/2023</t>
+  </si>
+  <si>
+    <t>Fondo de aportaciones múltiples (FAM)</t>
+  </si>
+  <si>
+    <t>Ejercicio y aplicación de los recursos públicos federales, de los capitulo 5000</t>
+  </si>
+  <si>
+    <t>Participaciones Federales</t>
+  </si>
+  <si>
+    <t>OFS/3651/2022</t>
+  </si>
+  <si>
     <t>Organo de fiscalización Superior del Estado de Tlaxcala</t>
   </si>
   <si>
+    <t>Orden de auditoría
+Oficio No. OFS/3651/2022</t>
+  </si>
+  <si>
     <t>Anexo I</t>
+  </si>
+  <si>
+    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2022.</t>
   </si>
   <si>
     <t>Artículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
@@ -285,35 +353,101 @@
 Remanentes de ejercicios anteriores y/o federales</t>
   </si>
   <si>
-    <t>Del 01/01/2022 al 31/12/2022</t>
-  </si>
-  <si>
-    <t>OFS/3651/2022</t>
+    <t>1893</t>
+  </si>
+  <si>
+    <t>Acta 2022-1893-AFITA</t>
+  </si>
+  <si>
+    <t>AEGF/3085/2023</t>
+  </si>
+  <si>
+    <t>Subisidios Federales para Organismos Descentralizados  Estatales, Politecnica y Pública con Apoyo Solidario (U006) de la Cuenta Pública 2022</t>
+  </si>
+  <si>
+    <t>OFS/1403/2023
+ Del 01 de Octubre al 31 de Diciembre 2022</t>
+  </si>
+  <si>
+    <t>Dirección Administrativa
+Subdirección de Servicios Administrativos
+Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>7C9CD084F810DCD631007A968F8A48E1</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>https://www.ofstlaxcala.gob.mx/transparencia/uploads/doc_ofs/XXV/inf_2022/estatales/entidades/6._Informe_COBAT_2022.pdf</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>02/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala,  se informa que con  fecha 10 de julio del 2023, el Organo de Fiscalización Superior del Estado de Tlaxcala, emite el Informe de Resultados Finales, en el cual se instruye al Órgano de Fiscalización Superior de seguimiento a las observaciones pendientes de solventar, dicho dictamen no modifica, solventa, limita o implica nulidad de las observaciones, que continuarán subsistentes, conforme al Informe en mención, por lo que los servidores públicos del Colegio de Bachilleres del Estado de Tlaxcala, estarán obligados a sujetarse a los procedimientos de responsabilidad administrativa y/o penales o cualquier otro que legalmente resulte procedente, de acuedo a lo establecido en el artículo 19 de la Constitución Política de los Estados Unidos Mexicanos.</t>
+  </si>
+  <si>
+    <t>32592D070D2F4844FFCC24474DF5113B</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención a la solicitud de información adicional, cabe señalar que se encuentra en culminada.</t>
+  </si>
+  <si>
+    <t>3E7892C8967E82B9F168B2857DBEBC2A</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención a la solicitud de información adicional, cabe señalar que se encuentra en proceso la auditoría mencionada.</t>
+  </si>
+  <si>
+    <t>7FB505B7190C01215B47201B704D9A74</t>
+  </si>
+  <si>
+    <t>99A6910C65A859C31BBAB8B05803C23C</t>
+  </si>
+  <si>
+    <t>Del 01/01/2023 al 31/12/2023</t>
+  </si>
+  <si>
+    <t>OFS/2255/2023</t>
   </si>
   <si>
     <t>Orden de auditoría
-Oficio No. OFS/3651/2022</t>
-  </si>
-  <si>
-    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2022.</t>
-  </si>
-  <si>
-    <t>A10A7E98B8DCCEFC08791D0EA9600645</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>03/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala,  atendió  la apertura de la auditoria  OFS/3651/2022 así como la integración de la información solicitada en el Anexo I, lo anterior para dar inicio a los trabajos de fiscalización para el ejercicio fiscal 2022.</t>
+Oficio No. OFS/2255/2023</t>
+  </si>
+  <si>
+    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2023.</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de enero de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora, toda vez que se encuentra en desarrollo los trabajos de revisión, motivo por el cual no se han emtido observaciones preliminares y/o resultados finales.</t>
   </si>
   <si>
     <t>Auditoría interna</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -706,10 +840,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -717,37 +851,38 @@
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="134.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="176.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="127.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="88" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="255" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="54.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="106.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="46" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="57.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="255" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="77.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -764,7 +899,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -779,7 +914,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -847,31 +982,34 @@
         <v>6</v>
       </c>
       <c r="X4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>10</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>11</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>10</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>7</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>12</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -962,10 +1100,13 @@
       <c r="AE5" t="s">
         <v>43</v>
       </c>
+      <c r="AF5" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -997,197 +1138,596 @@
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
     </row>
-    <row r="7" spans="1:31" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="T9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="X9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="AD9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="P10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF10" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>94</v>
+      <c r="P12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AE6"/>
+    <mergeCell ref="A6:AF6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1195,9 +1735,12 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G145">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G181">
       <formula1>Hidden_16</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X181">
+      <formula1>Hidden_223</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1211,12 +1754,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
